--- a/output/pdf_financials_xlsx/SPN.xlsx
+++ b/output/pdf_financials_xlsx/SPN.xlsx
@@ -5679,22 +5679,22 @@
         <v>5.279305</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.816463</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.90642</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.478898</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>6.853555</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>7.665945</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>7.941775</v>
       </c>
     </row>
     <row r="93">
@@ -10054,7 +10054,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -12190,7 +12194,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SPN.xlsx
+++ b/output/pdf_financials_xlsx/SPN.xlsx
@@ -1020,22 +1020,22 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001281</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.010919</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003054</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.006453</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.06472</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000467</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1053,16 +1053,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.054565</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.13183</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.190575</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.096718</v>
       </c>
     </row>
     <row r="13">
@@ -1915,22 +1915,22 @@
         <v>-0.034339</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.015738</v>
+        <v>-0.017019</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.237889</v>
+        <v>-2.248808</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.045089</v>
+        <v>-0.048143</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.564866</v>
+        <v>-2.571319</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-7.225334</v>
+        <v>-7.290054</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-17.145444</v>
+        <v>-17.145911</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-8.844258</v>
@@ -1948,16 +1948,16 @@
         <v>2.934313</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.758899</v>
+        <v>-2.813464</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-6.727375</v>
+        <v>-6.859205</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.975152</v>
+        <v>-2.165727</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-4.868552</v>
+        <v>-4.96527</v>
       </c>
     </row>
     <row r="28">
@@ -2025,22 +2025,22 @@
         <v>-0.034339</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.015738</v>
+        <v>-0.017019</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.223984</v>
+        <v>-2.234903</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.002268</v>
+        <v>-0.005322</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.493347</v>
+        <v>-2.4998</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-6.493356</v>
+        <v>-6.558076</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-15.672501</v>
+        <v>-15.672968</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-7.129919</v>
@@ -2058,16 +2058,16 @@
         <v>4.093878</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.672067</v>
+        <v>-1.726632</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.658665</v>
+        <v>-5.790495</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.818604</v>
+        <v>-1.009179</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.813452</v>
+        <v>-3.91017</v>
       </c>
     </row>
     <row r="30">
@@ -2092,16 +2092,16 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-0.2605638657199972</v>
+        <v>-0.6114289653270835</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-69.99762776719552</v>
+        <v>-70.17878774692628</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-54.61084818284859</v>
+        <v>-55.15516056836911</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-139.6372256737891</v>
+        <v>-139.641386502006</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-55.36073050284342</v>
@@ -2119,16 +2119,16 @@
         <v>28.51991245923304</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-6.779398573861446</v>
+        <v>-7.000632461727633</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-18.52474945339915</v>
+        <v>-18.95632080820485</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-3.601155144272937</v>
+        <v>-4.439521609156832</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-17.32521327067617</v>
+        <v>-17.76462091947134</v>
       </c>
     </row>
     <row r="31">
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.195351</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.060258</v>
@@ -2282,31 +2282,31 @@
         <v>2.375619</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.38663</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.594429</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.848719</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.916047</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.744618</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>5.550714</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.943006</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>3.704155</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>3.37268</v>
       </c>
     </row>
     <row r="35">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.195351</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.060258</v>
@@ -2392,31 +2392,31 @@
         <v>2.375619</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.38663</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.594429</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.848719</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.916047</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.744618</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>5.550714</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.943006</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>3.704155</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>3.37268</v>
       </c>
     </row>
     <row r="37">
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.053949</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.066876</v>
@@ -3052,31 +3052,31 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.700059</v>
+        <v>4.313429</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.015309</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.36342</v>
+        <v>2.514701</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.060875</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.408047</v>
+        <v>2.663429</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.00202</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>4.914799</v>
+        <v>1.210644</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>4.7058</v>
+        <v>1.33312</v>
       </c>
     </row>
     <row r="49">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -22586,7 +22586,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
@@ -35234,7 +35234,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -37864,7 +37864,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -40508,7 +40508,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -43188,7 +43188,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -44228,7 +44228,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -46296,7 +46296,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -47982,7 +47982,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -51178,7 +51178,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">

--- a/output/pdf_financials_xlsx/SPN.xlsx
+++ b/output/pdf_financials_xlsx/SPN.xlsx
@@ -2009,10 +2009,10 @@
         <v>1.06871</v>
       </c>
       <c r="P28" s="3" t="n">
+        <v>1.0551</v>
+      </c>
+      <c r="Q28" s="3" t="n">
         <v>1.156548</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>1.0551</v>
       </c>
     </row>
     <row r="29">
@@ -2064,10 +2064,10 @@
         <v>-5.790495</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.009179</v>
+        <v>-1.110627</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.91017</v>
+        <v>-3.808722</v>
       </c>
     </row>
     <row r="30">
@@ -2125,10 +2125,10 @@
         <v>-18.95632080820485</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-4.439521609156832</v>
+        <v>-4.885805755186171</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-17.76462091947134</v>
+        <v>-17.30372401139867</v>
       </c>
     </row>
     <row r="31">
@@ -6090,31 +6090,31 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>1.714339</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>1.952641</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>2.160987</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>1.578787</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>1.159565</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>1.086832</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>1.06871</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>1.156548</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>1.0551</v>
       </c>
     </row>
     <row r="101">
@@ -23354,7 +23354,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -24556,7 +24556,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -30038,7 +30042,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -34784,7 +34792,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -37526,7 +37534,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">

--- a/output/pdf_financials_xlsx/SPN.xlsx
+++ b/output/pdf_financials_xlsx/SPN.xlsx
@@ -6130,7 +6130,7 @@
         <v>0.016353</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.131814</v>
+        <v>-0.143192</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>-0.143327</v>
@@ -6405,7 +6405,7 @@
         <v>0.082747</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.067441</v>
+        <v>-0.078819</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.197351</v>
@@ -6634,7 +6634,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="H110" s="3" t="n">
         <v>0</v>
@@ -28052,7 +28052,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -29574,7 +29578,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -32524,7 +32532,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E263" s="5" t="n">
         <v>-0.006859</v>
       </c>
